--- a/test_doc/new_org/syllabus_7_mathematics.xlsx
+++ b/test_doc/new_org/syllabus_7_mathematics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,16 +441,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Integers</t>
+          <t>Mensuration</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Properties of integers</t>
+          <t>Perimeter</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Multiplication and division</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -471,16 +471,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fractions and Decimals</t>
+          <t>Simple Equations</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Multiplying fractions</t>
+          <t>Setting up equations</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -491,26 +491,26 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decimal operations</t>
+          <t>Solving equations</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Handling</t>
+          <t>The Triangle and Its Properties</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mean, median, mode</t>
+          <t>Medians and altitudes</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bar graphs and chance</t>
+          <t>Angle sum property</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -531,16 +531,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
+          <t>Data Handling</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Setting up equations</t>
+          <t>Pictographs and tally marks</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,11 +551,11 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Solving equations</t>
+          <t>Bar graphs</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>The Triangle and Its Properties</t>
+          <t>Basic Geometrical Ideas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medians and altitudes</t>
+          <t>Points, lines and curves</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,26 +611,26 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Angle sum property</t>
+          <t>Polygons and circles</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Comparing Quantities</t>
+          <t>Integers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Percentages</t>
+          <t>Negative numbers</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -641,11 +641,11 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Profit, loss and interest</t>
+          <t>Operations on integers</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Perimeter and Area</t>
+          <t>Ratio and Proportion</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Area of triangles</t>
+          <t>Ratio</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -701,26 +701,26 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Circles</t>
+          <t>Unitary method</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Algebraic Expressions</t>
+          <t>Decimals</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Terms and coefficients</t>
+          <t>Place value in decimals</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -731,40 +731,10 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adding expressions</t>
+          <t>Operations on decimals</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Exponents and Powers</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Laws of exponents</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Standard form</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
         <v>2</v>
       </c>
     </row>
